--- a/ITI/MHD/StructureDefinition-IHE.MHD.UnContained.Comprehensive.SubmissionSet.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.UnContained.Comprehensive.SubmissionSet.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$51</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="409">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.3</t>
+    <t>4.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T14:38:46-05:00</t>
+    <t>2026-06-15T14:55:16-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -650,6 +650,25 @@
 </t>
   </si>
   <si>
+    <t>List.extension:homeCommunityId</t>
+  </si>
+  <si>
+    <t>homeCommunityId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/ITI/MHD/StructureDefinition/ihe-HomeCommunityId}
+</t>
+  </si>
+  <si>
+    <t>The homeCommunityId where the artifact resides</t>
+  </si>
+  <si>
+    <t>The globally unique, immutable, identifier of the homeCommunityId entity where this artifact resides. The format of the value is an OID.</t>
+  </si>
+  <si>
+    <t>SubmissionSet.homeCommunityId</t>
+  </si>
+  <si>
     <t>List.extension:sourceId</t>
   </si>
   <si>
@@ -707,7 +726,7 @@
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:use}
+    <t xml:space="preserve">value:type}
 </t>
   </si>
   <si>
@@ -730,6 +749,12 @@
 </t>
   </si>
   <si>
+    <t>SubmissionSet.uniqueId</t>
+  </si>
+  <si>
+    <t>The XDS UniqueId for the SubmissionSet. Globally unique identifier for the SubmissionSet assigned by the creating entity.</t>
+  </si>
+  <si>
     <t>List.identifier:entryUUID</t>
   </si>
   <si>
@@ -738,6 +763,12 @@
   <si>
     <t xml:space="preserve">Identifier {https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.EntryUUID.Identifier}
 </t>
+  </si>
+  <si>
+    <t>SubmissionSet.entryUUID</t>
+  </si>
+  <si>
+    <t>The XDS entryUUID for the SubmissionSet. A globally unique identifier used to identify the XDS SubmissionSet in ebRIM.</t>
   </si>
   <si>
     <t>List.status</t>
@@ -1605,12 +1636,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM50"/>
+  <dimension ref="A1:AM51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.21875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.98046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="23.53125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.6640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -3659,7 +3690,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -3740,7 +3771,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>118</v>
@@ -3770,10 +3801,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -3871,9 +3902,11 @@
         <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>81</v>
       </c>
@@ -3882,25 +3915,25 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3951,7 +3984,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3966,7 +3999,7 @@
         <v>118</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
@@ -3977,10 +4010,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3991,25 +4024,25 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4048,17 +4081,19 @@
         <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4070,28 +4105,26 @@
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
+      <c r="A23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>223</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4100,10 +4133,10 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>81</v>
@@ -4112,13 +4145,13 @@
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4157,19 +4190,17 @@
         <v>81</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4184,24 +4215,24 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>81</v>
@@ -4211,7 +4242,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>90</v>
@@ -4223,13 +4254,13 @@
         <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4280,7 +4311,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4298,51 +4329,51 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM24" t="s" s="2">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
-      <c r="A25" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4352,7 +4383,7 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>233</v>
+        <v>81</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>81</v>
@@ -4367,13 +4398,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>236</v>
+        <v>81</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -4391,13 +4422,13 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
@@ -4406,21 +4437,21 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>237</v>
+        <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4446,17 +4477,15 @@
         <v>166</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
       </c>
@@ -4465,29 +4494,29 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="T26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>247</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
       </c>
@@ -4504,7 +4533,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>89</v>
@@ -4519,21 +4548,21 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>250</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4541,7 +4570,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
@@ -4550,21 +4579,23 @@
         <v>81</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>254</v>
       </c>
@@ -4576,10 +4607,10 @@
         <v>81</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>255</v>
+        <v>81</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>81</v>
@@ -4591,13 +4622,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>81</v>
+        <v>256</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -4615,10 +4646,10 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>89</v>
@@ -4630,21 +4661,21 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>81</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4652,7 +4683,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>89</v>
@@ -4667,19 +4698,17 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>259</v>
+        <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -4689,10 +4718,10 @@
         <v>81</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>81</v>
+        <v>265</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>81</v>
@@ -4704,11 +4733,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>265</v>
+        <v>81</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -4726,7 +4757,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4747,15 +4778,15 @@
         <v>267</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
         <v>268</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>269</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4769,7 +4800,7 @@
         <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>81</v>
@@ -4778,19 +4809,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -4800,7 +4831,7 @@
         <v>81</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>81</v>
@@ -4815,13 +4846,11 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -4839,7 +4868,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4854,21 +4883,21 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4876,31 +4905,35 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -4948,7 +4981,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4963,21 +4996,21 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>107</v>
+        <v>285</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4985,10 +5018,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
@@ -4997,23 +5030,19 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5061,7 +5090,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5076,35 +5105,35 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>290</v>
+        <v>107</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>81</v>
@@ -5174,7 +5203,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5198,7 +5227,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>303</v>
       </c>
@@ -5207,7 +5236,7 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5217,25 +5246,29 @@
         <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>103</v>
+        <v>305</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>104</v>
+        <v>306</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5283,7 +5316,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>106</v>
+        <v>303</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5295,35 +5328,35 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>107</v>
+        <v>311</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -5335,17 +5368,15 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5382,31 +5413,31 @@
         <v>81</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
@@ -5420,23 +5451,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -5448,15 +5477,17 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>307</v>
+        <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>111</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5493,16 +5524,16 @@
         <v>81</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>117</v>
@@ -5520,10 +5551,10 @@
         <v>118</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>310</v>
+        <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -5531,12 +5562,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>81</v>
       </c>
@@ -5554,20 +5587,18 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>317</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5616,25 +5647,25 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>117</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
@@ -5642,10 +5673,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5668,16 +5699,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5703,13 +5734,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>322</v>
+        <v>81</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -5727,7 +5758,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5736,7 +5767,7 @@
         <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>101</v>
@@ -5753,10 +5784,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5779,16 +5810,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>216</v>
+        <v>131</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5814,13 +5845,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>81</v>
+        <v>331</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>332</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5838,7 +5869,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5856,7 +5887,7 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>329</v>
+        <v>189</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
@@ -5864,10 +5895,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5890,16 +5921,16 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>103</v>
+        <v>222</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5949,7 +5980,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5967,7 +5998,7 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>189</v>
+        <v>339</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
@@ -5975,10 +6006,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5989,7 +6020,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -5998,23 +6029,21 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>259</v>
+        <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6038,13 +6067,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>340</v>
+        <v>81</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>341</v>
+        <v>81</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6062,7 +6091,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6077,10 +6106,10 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>342</v>
+        <v>189</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
@@ -6088,10 +6117,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6102,7 +6131,7 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6114,16 +6143,20 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>344</v>
+        <v>269</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6147,13 +6180,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>81</v>
+        <v>350</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>81</v>
+        <v>351</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6171,13 +6204,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6186,10 +6219,10 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>347</v>
+        <v>107</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
@@ -6197,10 +6230,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6211,7 +6244,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6223,17 +6256,15 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6282,7 +6313,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6291,16 +6322,16 @@
         <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>81</v>
+        <v>357</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
@@ -6308,10 +6339,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6322,7 +6353,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -6334,15 +6365,17 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>103</v>
+        <v>360</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>104</v>
+        <v>361</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6391,25 +6424,25 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>106</v>
+        <v>359</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>81</v>
+        <v>364</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>107</v>
+        <v>365</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -6417,21 +6450,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
@@ -6443,17 +6476,15 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6502,19 +6533,19 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -6528,14 +6559,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>359</v>
+        <v>109</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6548,26 +6579,24 @@
         <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>360</v>
+        <v>111</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>112</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O45" t="s" s="2">
-        <v>362</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -6615,7 +6644,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>363</v>
+        <v>117</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6633,7 +6662,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -6641,45 +6670,45 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>81</v>
+        <v>369</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>259</v>
+        <v>110</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>367</v>
+        <v>113</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -6704,13 +6733,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>369</v>
+        <v>81</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -6728,25 +6757,25 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>249</v>
+        <v>189</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -6754,10 +6783,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6774,76 +6803,74 @@
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>372</v>
+        <v>269</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M47" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q47" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="R47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6852,7 +6879,7 @@
         <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
@@ -6861,7 +6888,7 @@
         <v>107</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>379</v>
+        <v>259</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -6869,10 +6896,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6889,72 +6916,76 @@
         <v>81</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>285</v>
+        <v>382</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q48" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="R48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -6963,7 +6994,7 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
@@ -6972,7 +7003,7 @@
         <v>107</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -6980,10 +7011,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6991,10 +7022,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7006,16 +7037,18 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>386</v>
+        <v>295</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7063,10 +7096,10 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>89</v>
@@ -7078,10 +7111,10 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>389</v>
+        <v>107</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -7089,10 +7122,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7100,10 +7133,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7115,20 +7148,16 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>259</v>
+        <v>396</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7152,13 +7181,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>397</v>
+        <v>81</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7176,32 +7205,145 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK51" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AL51" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM50">
+  <autoFilter ref="A1:AM51">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7211,7 +7353,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI49">
+  <conditionalFormatting sqref="A2:AI50">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ITI/MHD/StructureDefinition-IHE.MHD.UnContained.Comprehensive.SubmissionSet.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.UnContained.Comprehensive.SubmissionSet.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.4</t>
+    <t>4.2.5-comment</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:55:16-05:00</t>
+    <t>2026-06-16T19:25:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
